--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -2400,7 +2400,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2418,7 +2418,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2438,7 +2442,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2456,11 +2460,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2560,15 +2560,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2580,7 +2576,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2640,11 +2636,15 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2982,11 +2982,15 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -3058,15 +3062,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3632,11 +3632,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3648,7 +3652,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3674,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3712,13 +3716,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3754,13 +3758,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3838,15 +3842,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3922,15 +3922,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3942,7 +3938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3964,11 +3960,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -4078,11 +4078,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -4094,7 +4098,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4120,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4154,15 +4158,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4530,11 +4530,15 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -4546,7 +4550,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4568,15 +4572,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4724,15 +4724,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -4742,7 +4738,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4762,11 +4762,15 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -4776,11 +4780,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -5488,22 +5488,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5512,7 +5504,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5534,20 +5526,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -5580,14 +5572,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5618,20 +5618,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -5664,14 +5664,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5680,7 +5688,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5702,22 +5710,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5748,26 +5748,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5776,7 +5772,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5798,22 +5794,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5894,22 +5894,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5918,7 +5922,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5940,26 +5944,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5990,22 +5990,26 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6014,7 +6018,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6036,26 +6040,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6086,22 +6086,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6110,7 +6118,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6132,20 +6140,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6178,20 +6186,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6224,22 +6232,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6248,7 +6264,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6270,20 +6286,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6316,27 +6332,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>7000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1680.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6370,20 +6386,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6416,20 +6432,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -6462,20 +6478,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6508,30 +6524,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -6540,7 +6548,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6562,20 +6570,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -6654,30 +6662,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7686,11 +7686,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7710,7 +7706,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7724,7 +7720,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8352,15 +8352,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -8370,7 +8366,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8428,11 +8428,15 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -8442,11 +8446,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8858,13 +8858,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -9018,13 +9018,13 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="G191" t="inlineStr"/>
@@ -9060,18 +9060,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -9080,7 +9084,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9102,22 +9106,18 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9148,20 +9148,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9194,20 +9194,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -9240,20 +9240,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J196" t="inlineStr"/>
@@ -9332,20 +9332,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9378,18 +9378,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
       <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
@@ -9398,7 +9402,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9420,22 +9424,18 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9815,7 +9815,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T15:16:11.078078</t>
+          <t>生成时间: 2026-06-12T16:09:12.748566</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -1738,7 +1738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:L143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3096,11 +3096,15 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3134,7 +3138,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3150,7 +3154,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3172,15 +3176,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3632,13 +3632,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3674,13 +3674,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3758,13 +3758,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3800,15 +3800,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3820,7 +3816,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3842,11 +3838,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3880,13 +3880,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3922,11 +3922,15 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3938,7 +3942,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3998,15 +4002,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4116,15 +4116,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4136,7 +4132,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4158,11 +4154,15 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4526,13 +4526,13 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>10377.0</t>
+          <t>1153.0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -4568,13 +4568,13 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1153.0</t>
+          <t>10377.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -4648,15 +4648,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -4666,7 +4662,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4724,11 +4724,15 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -4738,11 +4742,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4823,42 +4823,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>6999.972</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4866,49 +4854,37 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>2999.988</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>-0.012</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4916,49 +4892,37 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>1499.994</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4966,49 +4930,37 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5016,49 +4968,37 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5066,49 +5006,37 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>5000.0031</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>0.0031</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5116,49 +5044,37 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>3000.0012</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5166,49 +5082,37 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>2912.5034</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2912.5</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>0.0034</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5216,49 +5120,37 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>2000.0019</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>0.0019</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5266,99 +5158,75 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>1747.5007</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1747.5</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>0.0007</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.0%</t>
-        </is>
-      </c>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>999.9993</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>-0.0007</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5366,49 +5234,37 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>999.9993</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>-0.0007</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5416,49 +5272,37 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>339.999</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>340.0</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>-0.001</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5466,44 +5310,36 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1992-12-04</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5512,44 +5348,36 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1992-12-04</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5558,29 +5386,29 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1992-12-04</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -5603,22 +5431,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1992-12-04</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -5634,44 +5462,36 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1992-12-04</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5680,45 +5500,49 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>盛祎等15名自然人</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5726,47 +5550,35 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.9%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
@@ -5776,47 +5588,35 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>盛祎</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
@@ -5833,37 +5633,29 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5872,44 +5664,40 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5918,47 +5706,35 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -5968,44 +5744,36 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6021,40 +5789,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
+          <t>牛威(罗永红代持)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
@@ -6071,37 +5831,33 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6110,42 +5866,42 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6163,37 +5919,33 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
@@ -6202,52 +5954,44 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6256,52 +6000,44 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>策星揽月</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6310,42 +6046,42 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -6363,35 +6099,35 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6409,37 +6145,33 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -6448,42 +6180,42 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6501,35 +6233,35 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -6547,46 +6279,42 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6594,45 +6322,49 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>策星九天 (认缴→存量)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr"/>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6640,45 +6372,49 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>幸福一期 (认缴→存量)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr"/>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6686,42 +6422,42 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司 (认缴→存量)</t>
+          <t>策星揽月 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6743,35 +6479,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>幸福二期 (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6793,35 +6529,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>策星银河 (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6843,35 +6579,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>罗世兵 (认缴→存量)</t>
+          <t>策星逐日 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6890,2932 +6626,24 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 14 条</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 14 条</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>周乃鼎</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Cheer Rise Consultants Limited</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>黄学英/刘鸿雁</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>史建伟</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>深圳中证投资有限责任公司</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>北京岚锋创视网络科技有限公司</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>香港迅雷有限公司</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>QM101 Limited</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>EARN ACE LIMITED</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>香港迅雷有限公司</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>北京岚锋创视网络科技有限公司</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>QM101 Limited</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>EARN ACE LIMITED</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>香港迅雷有限公司</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>北京岚锋创视网络科技有限公司</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>QM101 Limited</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>EARN ACE LIMITED</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>盛祎等15名自然人</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2002-11-07</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>朱绶青</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>2002-11-07</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>2002-11-07</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>盛祎</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>牛威(罗永红代持)</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>吴功友(王金林代持)</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>四方股份</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>幸福二期</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>策星银河</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>策星逐日</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>策星揽月</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>幸福一期</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>策星九天</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>中科星图股份有限公司</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>策星九天 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>幸福一期 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>策星揽月 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr"/>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>幸福二期 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr"/>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>策星银河 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>策星逐日 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 14 条</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 14 条</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>生成时间: 2026-06-12T16:30:01.183788</t>
+          <t>生成时间: 2026-06-12T17:00:58.845054</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
+++ b/outputs/week2_excel/688775_影石创新_三表抽取.xlsx
@@ -2480,11 +2480,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2496,7 +2500,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2556,15 +2560,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3058,11 +3058,15 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -3096,7 +3100,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3134,15 +3138,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3632,13 +3632,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3674,11 +3674,15 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3690,7 +3694,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3712,13 +3716,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3754,13 +3758,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3796,13 +3800,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3838,13 +3842,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3880,15 +3884,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4488,15 +4488,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4508,7 +4504,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4530,11 +4526,15 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -5488,14 +5488,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5504,7 +5512,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5526,22 +5534,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5572,22 +5572,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5596,7 +5588,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5618,20 +5610,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -5664,14 +5656,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5748,20 +5748,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -5794,22 +5794,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -5818,7 +5822,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5840,26 +5844,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5890,22 +5890,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5914,7 +5918,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5936,23 +5940,23 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -5986,26 +5990,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6086,20 +6086,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6132,20 +6132,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6178,20 +6178,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6224,20 +6224,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6270,30 +6270,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6302,7 +6294,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6324,27 +6316,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>7000.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1680.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6378,20 +6370,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6424,22 +6416,30 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6470,20 +6470,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6516,27 +6516,27 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>1680.0</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -6570,20 +6570,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -6616,20 +6616,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -6662,20 +6662,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7876,11 +7876,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7900,7 +7896,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7938,7 +7934,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7952,7 +7948,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -8428,7 +8428,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>待复核</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8858,13 +8858,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -8900,15 +8900,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
@@ -8920,7 +8916,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8980,11 +8976,15 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
@@ -8996,7 +8996,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -9060,22 +9060,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -9084,7 +9080,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9106,20 +9102,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
@@ -9152,20 +9148,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9198,18 +9194,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
       <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9240,18 +9240,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -9260,7 +9264,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9282,22 +9286,18 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9328,20 +9328,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -9420,20 +9420,20 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -9815,7 +9815,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:05:42.726772</t>
+          <t>生成时间: 2026-06-12T17:10:43.436789</t>
         </is>
       </c>
     </row>
